--- a/DISASTER/communities_affected_by_erosion.xlsx
+++ b/DISASTER/communities_affected_by_erosion.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="20">
   <si>
     <t>lga_id</t>
   </si>
@@ -40,12 +40,10 @@
     <t>Amachalla, Awka</t>
   </si>
   <si>
-    <t>Federal High Court/Ekwueme Square,
-Awka (Palliative)</t>
-  </si>
-  <si>
-    <t>Neroz Plaza/ St Thomas Aquinas
-Community, Awka</t>
+    <t>Federal High Court/Ekwueme Square, Awka (Palliative)</t>
+  </si>
+  <si>
+    <t>Neroz Plaza/ St Thomas Aquinas Community, Awka</t>
   </si>
   <si>
     <t>Ugamuma Village, Obosi</t>
@@ -76,12 +74,6 @@
   </si>
   <si>
     <t>New Heritage/Omagba, Onitsha</t>
-  </si>
-  <si>
-    <t>Federal High Court/Ekwueme Square, Awka (Palliative)</t>
-  </si>
-  <si>
-    <t>Neroz Plaza/ St Thomas Aquinas Community, Awka</t>
   </si>
 </sst>
 </file>
@@ -795,7 +787,7 @@
         <v>2020</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D16">
         <v>26.6</v>
@@ -818,7 +810,7 @@
         <v>2020</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D17">
         <v>16.8</v>

--- a/DISASTER/communities_affected_by_erosion.xlsx
+++ b/DISASTER/communities_affected_by_erosion.xlsx
@@ -477,7 +477,7 @@
         <v>46.3</v>
       </c>
       <c r="G2">
-        <v>97.5</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -500,7 +500,7 @@
         <v>26.6</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -523,7 +523,7 @@
         <v>16.8</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -546,7 +546,7 @@
         <v>41.3</v>
       </c>
       <c r="G5">
-        <v>17.71</v>
+        <v>0.1771</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -569,7 +569,7 @@
         <v>80.90000000000001</v>
       </c>
       <c r="G6">
-        <v>49</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -592,7 +592,7 @@
         <v>66.40000000000001</v>
       </c>
       <c r="G7">
-        <v>46.40000000000001</v>
+        <v>0.464</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -615,7 +615,7 @@
         <v>482.8</v>
       </c>
       <c r="G8">
-        <v>68</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -638,7 +638,7 @@
         <v>88.5</v>
       </c>
       <c r="G9">
-        <v>53</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -661,7 +661,7 @@
         <v>355.7</v>
       </c>
       <c r="G10">
-        <v>38</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -684,7 +684,7 @@
         <v>171.8</v>
       </c>
       <c r="G11">
-        <v>38</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -707,7 +707,7 @@
         <v>15.1</v>
       </c>
       <c r="G12">
-        <v>14</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -730,7 +730,7 @@
         <v>433.6</v>
       </c>
       <c r="G13">
-        <v>38</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -753,7 +753,7 @@
         <v>74.7</v>
       </c>
       <c r="G14">
-        <v>94</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -776,7 +776,7 @@
         <v>47.5</v>
       </c>
       <c r="G15">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -799,7 +799,7 @@
         <v>26.6</v>
       </c>
       <c r="G16">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -822,7 +822,7 @@
         <v>16.8</v>
       </c>
       <c r="G17">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -845,7 +845,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="G18">
-        <v>38.9</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -868,7 +868,7 @@
         <v>110.6</v>
       </c>
       <c r="G19">
-        <v>67</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -891,7 +891,7 @@
         <v>74.40000000000001</v>
       </c>
       <c r="G20">
-        <v>52.02</v>
+        <v>0.5202</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -914,7 +914,7 @@
         <v>625.2</v>
       </c>
       <c r="G21">
-        <v>88.05</v>
+        <v>0.8804999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -937,7 +937,7 @@
         <v>89.3</v>
       </c>
       <c r="G22">
-        <v>53.5</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -960,7 +960,7 @@
         <v>749</v>
       </c>
       <c r="G23">
-        <v>80</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -983,7 +983,7 @@
         <v>239.6</v>
       </c>
       <c r="G24">
-        <v>53</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1006,7 +1006,7 @@
         <v>21.6</v>
       </c>
       <c r="G25">
-        <v>20</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1029,7 +1029,7 @@
         <v>890</v>
       </c>
       <c r="G26">
-        <v>78</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1052,7 +1052,7 @@
         <v>77.3</v>
       </c>
       <c r="G27">
-        <v>97.2</v>
+        <v>0.972</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1075,7 +1075,7 @@
         <v>47.5</v>
       </c>
       <c r="G28">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1098,7 +1098,7 @@
         <v>26.6</v>
       </c>
       <c r="G29">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1121,7 +1121,7 @@
         <v>16.8</v>
       </c>
       <c r="G30">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1144,7 +1144,7 @@
         <v>107.9</v>
       </c>
       <c r="G31">
-        <v>41.94</v>
+        <v>0.4194</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1167,7 +1167,7 @@
         <v>110.6</v>
       </c>
       <c r="G32">
-        <v>67</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1190,7 +1190,7 @@
         <v>74.40000000000001</v>
       </c>
       <c r="G33">
-        <v>52.02</v>
+        <v>0.5202</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1213,7 +1213,7 @@
         <v>710</v>
       </c>
       <c r="G34">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1236,7 +1236,7 @@
         <v>100</v>
       </c>
       <c r="G35">
-        <v>60</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1259,7 +1259,7 @@
         <v>936</v>
       </c>
       <c r="G36">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1282,7 +1282,7 @@
         <v>312</v>
       </c>
       <c r="G37">
-        <v>69</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1305,7 +1305,7 @@
         <v>106</v>
       </c>
       <c r="G38">
-        <v>99</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1328,7 +1328,7 @@
         <v>1067</v>
       </c>
       <c r="G39">
-        <v>93.5</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1351,7 +1351,7 @@
         <v>79</v>
       </c>
       <c r="G40">
-        <v>9940</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1374,7 +1374,7 @@
         <v>47.5</v>
       </c>
       <c r="G41">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1397,7 +1397,7 @@
         <v>26.6</v>
       </c>
       <c r="G42">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1420,7 +1420,7 @@
         <v>16.8</v>
       </c>
       <c r="G43">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1443,7 +1443,7 @@
         <v>128.2</v>
       </c>
       <c r="G44">
-        <v>55.00000000000001</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1466,7 +1466,7 @@
         <v>157</v>
       </c>
       <c r="G45">
-        <v>80</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1489,7 +1489,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="G46">
-        <v>57.99999999999999</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1512,7 +1512,7 @@
         <v>710</v>
       </c>
       <c r="G47">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1535,7 +1535,7 @@
         <v>116.9</v>
       </c>
       <c r="G48">
-        <v>70</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1558,7 +1558,7 @@
         <v>936</v>
       </c>
       <c r="G49">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1581,7 +1581,7 @@
         <v>321</v>
       </c>
       <c r="G50">
-        <v>71</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1604,7 +1604,7 @@
         <v>108</v>
       </c>
       <c r="G51">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1627,7 +1627,7 @@
         <v>1141</v>
       </c>
       <c r="G52">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1650,7 +1650,7 @@
         <v>79.5</v>
       </c>
       <c r="G53">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
